--- a/docs/demo-materials/contract-sample-tests/合同样例-测试导入样本-重复.xlsx
+++ b/docs/demo-materials/contract-sample-tests/合同样例-测试导入样本-重复.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入样本" sheetId="1" r:id="R4910df1f6aad464c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入样本" sheetId="1" r:id="R2555719e1c8640b3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -346,7 +346,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d262d2780434311"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f1d1a1bc93246ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>